--- a/docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/docs/Lab01/Lab01_ReviewReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Miha\Desktop\VVSS\DrinkShopGit\docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A4CE3A-A6BF-4017-ACA1-B654026BEC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88939158-34B2-46C7-BD35-DC0D2C2E65C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2460" windowWidth="20064" windowHeight="9780" tabRatio="650" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="650" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -279,15 +282,9 @@
     <t>Reteta si Produs nu au o corelatie asa ca nu se pot prepara produse dupa reteta</t>
   </si>
   <si>
-    <t>DrinkShopService incalca DRY,are metode pe care le au si service-urile care il compun</t>
-  </si>
-  <si>
     <t>Repository are un nume prea general,poate fi Irepository sau RepositoryInterface</t>
   </si>
   <si>
-    <t>A01</t>
-  </si>
-  <si>
     <t>String.isEmpty()" should be used to test for emptiness</t>
   </si>
   <si>
@@ -352,19 +349,41 @@
   </si>
   <si>
     <t>nu avem posibilitatea de a afisa stocul (se cere la punctul 5 din requirements)</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Validarile exista dar nu sunt folosite explicit clasele respective</t>
+  </si>
+  <si>
+    <t>Taran Sergiu</t>
+  </si>
+  <si>
+    <t>Tibil Oana</t>
+  </si>
+  <si>
+    <t>30m</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -557,84 +576,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -653,9 +673,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -693,9 +713,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -728,9 +748,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -763,9 +800,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -968,12 +1022,12 @@
       <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -993,10 +1047,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="28"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
@@ -1007,10 +1061,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="30"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1269,12 +1323,12 @@
       <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1287,31 +1341,39 @@
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="I3" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" s="16">
+        <v>237</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="34"/>
+      <c r="E4" s="31"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="3">
+        <v>237</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="36"/>
+      <c r="E5" s="33"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1395,11 +1457,11 @@
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1412,7 +1474,7 @@
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1528,7 +1590,9 @@
         <v>8</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1574,12 +1638,12 @@
       <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1592,31 +1656,39 @@
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="I3" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" s="16">
+        <v>237</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="27"/>
+      <c r="E4" s="34"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="3">
+        <v>237</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="36"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1783,7 +1855,7 @@
         <v>53</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1984,12 +2056,12 @@
       <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -2002,20 +2074,28 @@
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="I3" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" s="16">
+        <v>237</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="3">
+        <v>237</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
@@ -2060,16 +2140,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -2078,16 +2158,16 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
@@ -2096,16 +2176,16 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="72" x14ac:dyDescent="0.3">
@@ -2114,16 +2194,16 @@
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -2132,16 +2212,16 @@
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -2306,7 +2386,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C32" s="37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D32" s="38"/>
       <c r="E32" s="38"/>
